--- a/output/Data and Chart Outputs/nigeria_power_generation_quarterly.xlsx
+++ b/output/Data and Chart Outputs/nigeria_power_generation_quarterly.xlsx
@@ -1047,7 +1047,7 @@
         <v>7984.68</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6163</v>
+        <v>3.6162</v>
       </c>
       <c r="H4" t="n">
         <v>2208</v>
@@ -2734,7 +2734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2763,6 +2763,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2823,6 +2828,9 @@
           <t>page 25; 28 plants; plant sum vs Total 0.000%; stated 8,883.47 GWh vs calc 8,883.48</t>
         </is>
       </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2853,6 +2861,9 @@
           <t>page 25; 28 plants; plant sum vs Total 0.000%; stated 9,831.58 GWh vs calc 9,831.58</t>
         </is>
       </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2883,6 +2894,9 @@
           <t>page 26; 28 plants; plant sum vs Total 0.000%; stated 9,227.57 GWh vs calc 9,227.56</t>
         </is>
       </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2913,6 +2927,9 @@
           <t>page 26; 28 plants; plant sum vs Total 0.000%; stated 9,830.31 GWh vs calc 9,830.32</t>
         </is>
       </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2943,6 +2960,9 @@
           <t>page 26; 28 plants; plant sum vs Total 0.000%; stated 10,304.47 GWh vs calc 10,304.47</t>
         </is>
       </c>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2973,6 +2993,9 @@
           <t>page 26; 28 plants; plant sum vs Total 0.000%; stated 9,289.95 GWh vs calc 9,289.96</t>
         </is>
       </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3003,6 +3026,9 @@
           <t>page 27; 28 plants; plant sum vs Total 0.000%; stated 9,450.76 GWh vs calc 9,450.77</t>
         </is>
       </c>
+      <c r="G9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3033,6 +3059,9 @@
           <t>key facts text: total 8,776.55 GWh, hydro share 26.98%</t>
         </is>
       </c>
+      <c r="G10" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -3063,6 +3092,9 @@
           <t>key facts text: total 8,887.93 GWh, hydro share 25.95%</t>
         </is>
       </c>
+      <c r="G11" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -3093,6 +3125,9 @@
           <t>key facts text: total 9,789.87 GWh, hydro share 27.61%</t>
         </is>
       </c>
+      <c r="G12" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -3123,6 +3158,9 @@
           <t>key facts text: total 8,664.28 GWh, hydro share 25.49%</t>
         </is>
       </c>
+      <c r="G13" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3153,6 +3191,9 @@
           <t>key facts text: total 8,867.05 GWh, hydro share 20.29%</t>
         </is>
       </c>
+      <c r="G14" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -3183,6 +3224,9 @@
           <t>key facts text: total 9,350.24 GWh, hydro share 25.35%</t>
         </is>
       </c>
+      <c r="G15" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3213,6 +3257,9 @@
           <t>key facts text: total 9,365.65 GWh, hydro share 31.1%</t>
         </is>
       </c>
+      <c r="G16" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3243,6 +3290,9 @@
           <t>key facts text: total 8,540.44 GWh, hydro share 29.42%</t>
         </is>
       </c>
+      <c r="G17" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3273,6 +3323,9 @@
           <t>key facts text: total 7,766.66 GWh, hydro share 18.56%</t>
         </is>
       </c>
+      <c r="G18" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3303,6 +3356,9 @@
           <t>key facts text: total 8,848.04 GWh, hydro share 26.56%</t>
         </is>
       </c>
+      <c r="G19" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3333,6 +3389,9 @@
           <t>key facts text: total 8,693.77 GWh, hydro share 30.39%</t>
         </is>
       </c>
+      <c r="G20" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3388,6 +3447,9 @@
           <t>key facts text: total 9,498.79 GWh, hydro share n/a%</t>
         </is>
       </c>
+      <c r="G22" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3418,6 +3480,9 @@
           <t>key facts text: total 9,628.20 GWh, hydro share n/a%</t>
         </is>
       </c>
+      <c r="G23" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3448,6 +3513,9 @@
           <t>key facts text: total 8,265.42 GWh, hydro share n/a%</t>
         </is>
       </c>
+      <c r="G24" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3478,6 +3546,9 @@
           <t>key facts text: total 8,734.93 GWh, hydro share n/a%</t>
         </is>
       </c>
+      <c r="G25" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3508,6 +3579,9 @@
           <t>key facts text: total 8,614.00 GWh, hydro share n/a%</t>
         </is>
       </c>
+      <c r="G26" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3538,6 +3612,9 @@
           <t>key facts text: total 8,101.19 GWh, hydro share n/a%</t>
         </is>
       </c>
+      <c r="G27" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3568,6 +3645,9 @@
           <t>key facts text: total 7,984.69 GWh, hydro share n/a%</t>
         </is>
       </c>
+      <c r="G28" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3598,6 +3678,9 @@
           <t>key facts text: total 8,451.43 GWh, hydro share n/a%</t>
         </is>
       </c>
+      <c r="G29" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3627,6 +3710,9 @@
         <is>
           <t>key facts text: total 8,951.87 GWh, hydro share n/a%</t>
         </is>
+      </c>
+      <c r="G30" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="31">

--- a/output/Data and Chart Outputs/nigeria_power_generation_quarterly.xlsx
+++ b/output/Data and Chart Outputs/nigeria_power_generation_quarterly.xlsx
@@ -2734,7 +2734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2765,6 +2765,11 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.1</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Unnamed: 0</t>
         </is>
       </c>
@@ -2831,6 +2836,9 @@
       <c r="G3" t="n">
         <v>1</v>
       </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2864,6 +2872,9 @@
       <c r="G4" t="n">
         <v>2</v>
       </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2897,6 +2908,9 @@
       <c r="G5" t="n">
         <v>3</v>
       </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2930,6 +2944,9 @@
       <c r="G6" t="n">
         <v>4</v>
       </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2963,6 +2980,9 @@
       <c r="G7" t="n">
         <v>5</v>
       </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2996,6 +3016,9 @@
       <c r="G8" t="n">
         <v>6</v>
       </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3029,6 +3052,9 @@
       <c r="G9" t="n">
         <v>7</v>
       </c>
+      <c r="H9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3062,6 +3088,9 @@
       <c r="G10" t="n">
         <v>8</v>
       </c>
+      <c r="H10" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -3095,6 +3124,9 @@
       <c r="G11" t="n">
         <v>9</v>
       </c>
+      <c r="H11" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -3128,6 +3160,9 @@
       <c r="G12" t="n">
         <v>10</v>
       </c>
+      <c r="H12" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -3161,6 +3196,9 @@
       <c r="G13" t="n">
         <v>11</v>
       </c>
+      <c r="H13" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3194,6 +3232,9 @@
       <c r="G14" t="n">
         <v>12</v>
       </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -3227,6 +3268,9 @@
       <c r="G15" t="n">
         <v>13</v>
       </c>
+      <c r="H15" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3260,6 +3304,9 @@
       <c r="G16" t="n">
         <v>14</v>
       </c>
+      <c r="H16" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3293,6 +3340,9 @@
       <c r="G17" t="n">
         <v>15</v>
       </c>
+      <c r="H17" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3326,6 +3376,9 @@
       <c r="G18" t="n">
         <v>16</v>
       </c>
+      <c r="H18" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3359,6 +3412,9 @@
       <c r="G19" t="n">
         <v>17</v>
       </c>
+      <c r="H19" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3392,6 +3448,9 @@
       <c r="G20" t="n">
         <v>18</v>
       </c>
+      <c r="H20" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3450,6 +3509,9 @@
       <c r="G22" t="n">
         <v>20</v>
       </c>
+      <c r="H22" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3483,6 +3545,9 @@
       <c r="G23" t="n">
         <v>21</v>
       </c>
+      <c r="H23" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3516,6 +3581,9 @@
       <c r="G24" t="n">
         <v>22</v>
       </c>
+      <c r="H24" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3549,6 +3617,9 @@
       <c r="G25" t="n">
         <v>23</v>
       </c>
+      <c r="H25" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3582,6 +3653,9 @@
       <c r="G26" t="n">
         <v>24</v>
       </c>
+      <c r="H26" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3615,6 +3689,9 @@
       <c r="G27" t="n">
         <v>25</v>
       </c>
+      <c r="H27" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3648,6 +3725,9 @@
       <c r="G28" t="n">
         <v>26</v>
       </c>
+      <c r="H28" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3681,6 +3761,9 @@
       <c r="G29" t="n">
         <v>27</v>
       </c>
+      <c r="H29" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3714,6 +3797,9 @@
       <c r="G30" t="n">
         <v>28</v>
       </c>
+      <c r="H30" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3739,6 +3825,9 @@
           <t>skipped: pre-2019 layout, quarter not reliably identified</t>
         </is>
       </c>
+      <c r="G31" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3764,6 +3853,9 @@
           <t>skipped: pre-2019 layout, quarter not reliably identified</t>
         </is>
       </c>
+      <c r="G32" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3789,6 +3881,9 @@
           <t>skipped: pre-2019 layout, quarter not reliably identified</t>
         </is>
       </c>
+      <c r="G33" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3814,6 +3909,9 @@
           <t>skipped: pre-2019 layout, quarter not reliably identified</t>
         </is>
       </c>
+      <c r="G34" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3839,6 +3937,9 @@
           <t>skipped: pre-2019 layout, quarter not reliably identified</t>
         </is>
       </c>
+      <c r="G35" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3863,6 +3964,9 @@
         <is>
           <t>skipped: pre-2019 layout, quarter not reliably identified</t>
         </is>
+      </c>
+      <c r="G36" t="n">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
